--- a/docs/proposal/SnapCare_도표_원자료.xlsx
+++ b/docs/proposal/SnapCare_도표_원자료.xlsx
@@ -8,13 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽는 법" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림1_문해율" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림2_건강문해력" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림3_조제오류" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림4_스마트폰" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림5_픽토그램" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림15_형성평가" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림17_모델오차" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림2_문해율" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림3_건강문해력" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림4_조제오류" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림8_스마트폰" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림10_픽토그램" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림32_형성평가" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림35_모델오차" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -187,7 +187,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'그림1_문해율'!B4</f>
+              <f>'그림2_문해율'!B4</f>
             </strRef>
           </tx>
           <spPr>
@@ -197,12 +197,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'그림1_문해율'!$A$5:$A$6</f>
+              <f>'그림2_문해율'!$A$5:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'그림1_문해율'!$B$5:$B$6</f>
+              <f>'그림2_문해율'!$B$5:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -211,7 +211,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'그림1_문해율'!C4</f>
+              <f>'그림2_문해율'!C4</f>
             </strRef>
           </tx>
           <spPr>
@@ -221,12 +221,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'그림1_문해율'!$A$5:$A$6</f>
+              <f>'그림2_문해율'!$A$5:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'그림1_문해율'!$C$5:$C$6</f>
+              <f>'그림2_문해율'!$C$5:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -297,7 +297,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'그림2_건강문해력'!B4</f>
+              <f>'그림3_건강문해력'!B4</f>
             </strRef>
           </tx>
           <spPr>
@@ -307,12 +307,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'그림2_건강문해력'!$A$5:$A$8</f>
+              <f>'그림3_건강문해력'!$A$5:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'그림2_건강문해력'!$B$5:$B$8</f>
+              <f>'그림3_건강문해력'!$B$5:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -383,7 +383,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'그림3_조제오류'!B4</f>
+              <f>'그림4_조제오류'!B4</f>
             </strRef>
           </tx>
           <spPr>
@@ -393,12 +393,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'그림3_조제오류'!$A$5:$A$8</f>
+              <f>'그림4_조제오류'!$A$5:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'그림3_조제오류'!$B$5:$B$8</f>
+              <f>'그림4_조제오류'!$B$5:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -407,7 +407,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'그림3_조제오류'!C4</f>
+              <f>'그림4_조제오류'!C4</f>
             </strRef>
           </tx>
           <spPr>
@@ -417,12 +417,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'그림3_조제오류'!$A$5:$A$8</f>
+              <f>'그림4_조제오류'!$A$5:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'그림3_조제오류'!$C$5:$C$8</f>
+              <f>'그림4_조제오류'!$C$5:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -493,7 +493,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'그림4_스마트폰'!B4</f>
+              <f>'그림8_스마트폰'!B4</f>
             </strRef>
           </tx>
           <spPr>
@@ -503,12 +503,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'그림4_스마트폰'!$A$5:$A$7</f>
+              <f>'그림8_스마트폰'!$A$5:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'그림4_스마트폰'!$B$5:$B$7</f>
+              <f>'그림8_스마트폰'!$B$5:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -579,7 +579,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'그림5_픽토그램'!B4</f>
+              <f>'그림10_픽토그램'!B4</f>
             </strRef>
           </tx>
           <spPr>
@@ -589,12 +589,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'그림5_픽토그램'!$A$5:$A$9</f>
+              <f>'그림10_픽토그램'!$A$5:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'그림5_픽토그램'!$B$5:$B$9</f>
+              <f>'그림10_픽토그램'!$B$5:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -603,7 +603,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'그림5_픽토그램'!C4</f>
+              <f>'그림10_픽토그램'!C4</f>
             </strRef>
           </tx>
           <spPr>
@@ -613,12 +613,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'그림5_픽토그램'!$A$5:$A$9</f>
+              <f>'그림10_픽토그램'!$A$5:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'그림5_픽토그램'!$C$5:$C$9</f>
+              <f>'그림10_픽토그램'!$C$5:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -689,7 +689,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'그림15_형성평가'!B4</f>
+              <f>'그림32_형성평가'!B4</f>
             </strRef>
           </tx>
           <spPr>
@@ -699,12 +699,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'그림15_형성평가'!$A$5:$A$6</f>
+              <f>'그림32_형성평가'!$A$5:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'그림15_형성평가'!$B$5:$B$6</f>
+              <f>'그림32_형성평가'!$B$5:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -713,7 +713,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'그림15_형성평가'!C4</f>
+              <f>'그림32_형성평가'!C4</f>
             </strRef>
           </tx>
           <spPr>
@@ -723,12 +723,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'그림15_형성평가'!$A$5:$A$6</f>
+              <f>'그림32_형성평가'!$A$5:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'그림15_형성평가'!$C$5:$C$6</f>
+              <f>'그림32_형성평가'!$C$5:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -799,7 +799,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'그림17_모델오차'!B4</f>
+              <f>'그림35_모델오차'!B4</f>
             </strRef>
           </tx>
           <spPr>
@@ -809,12 +809,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'그림17_모델오차'!$A$5:$A$9</f>
+              <f>'그림35_모델오차'!$A$5:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'그림17_모델오차'!$B$5:$B$9</f>
+              <f>'그림35_모델오차'!$B$5:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -823,7 +823,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'그림17_모델오차'!C4</f>
+              <f>'그림35_모델오차'!C4</f>
             </strRef>
           </tx>
           <spPr>
@@ -833,12 +833,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'그림17_모델오차'!$A$5:$A$9</f>
+              <f>'그림35_모델오차'!$A$5:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'그림17_모델오차'!$C$5:$C$9</f>
+              <f>'그림35_모델오차'!$C$5:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -1453,7 +1453,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>[그림 1] 사하라이남 아프리카의 문해율과 비문해 인구</t>
+          <t>[그림 2] 사하라이남 아프리카의 문해율과 비문해 인구</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>[그림 2] 건강정보이해능력이 충분하지 않은 비율 (한국)</t>
+          <t>[그림 3] 건강정보이해능력이 충분하지 않은 비율 (한국)</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>[그림 3] 조제 오류의 유형별 분포 (약사가 발견한 155건)</t>
+          <t>[그림 4] 조제 오류의 유형별 분포 (약사가 발견한 155건)</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>[그림 4] 연령대별 스마트폰 보유율 (미국, 2025)</t>
+          <t>[그림 8] 연령대별 스마트폰 보유율 (미국, 2025)</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>[그림 5] 의약 픽토그램이 이해도 기준을 통과한 비율</t>
+          <t>[그림 10] 의약 픽토그램이 이해도 기준을 통과한 비율</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>[그림 15] 형성 평가 — 수정 전후 (28회 시행)</t>
+          <t>[그림 32] 형성 평가 — 수정 전후 (28회 시행)</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>[그림 17] 영양 추정 모델의 항목별 오차 (n = 507)</t>
+          <t>[그림 35] 영양 추정 모델의 항목별 오차 (n = 507)</t>
         </is>
       </c>
     </row>
